--- a/R_Codes/DataSummary/Archaea/Sample_Type/Archaea_Summary_Phylum_by_Sample_Type.xlsx
+++ b/R_Codes/DataSummary/Archaea/Sample_Type/Archaea_Summary_Phylum_by_Sample_Type.xlsx
@@ -420,10 +420,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>18.6367855516225</v>
+        <v>18.6381271274119</v>
       </c>
       <c r="D2" t="n">
-        <v>1.01391049972148</v>
+        <v>1.01399917766499</v>
       </c>
     </row>
     <row r="3">
@@ -434,10 +434,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>18.5202533685736</v>
+        <v>18.5201013097571</v>
       </c>
       <c r="D3" t="n">
-        <v>0.505976770488784</v>
+        <v>0.505976909932865</v>
       </c>
     </row>
     <row r="4">
@@ -448,10 +448,10 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>16.8253760374375</v>
+        <v>16.821080099086</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8292262726294</v>
+        <v>2.82827026926379</v>
       </c>
     </row>
     <row r="5">
@@ -462,10 +462,10 @@
         <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>12.7949943573805</v>
+        <v>12.7953779007157</v>
       </c>
       <c r="D5" t="n">
-        <v>0.416981391722336</v>
+        <v>0.41699354510049</v>
       </c>
     </row>
     <row r="6">
@@ -476,10 +476,10 @@
         <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>11.7452341318612</v>
+        <v>11.7458348323098</v>
       </c>
       <c r="D6" t="n">
-        <v>1.37682566368649</v>
+        <v>1.37689345146925</v>
       </c>
     </row>
     <row r="7">
@@ -490,10 +490,10 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>6.95538214449839</v>
+        <v>6.95653878385309</v>
       </c>
       <c r="D7" t="n">
-        <v>0.051641360466749</v>
+        <v>0.0516579124591188</v>
       </c>
     </row>
     <row r="8">
@@ -504,10 +504,10 @@
         <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>6.11588517287203</v>
+        <v>6.1164324484389</v>
       </c>
       <c r="D8" t="n">
-        <v>0.616074763446808</v>
+        <v>0.616147299562352</v>
       </c>
     </row>
     <row r="9">
@@ -518,10 +518,10 @@
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>3.26312227248418</v>
+        <v>3.26300971531625</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0961006824323567</v>
+        <v>0.0960943283127623</v>
       </c>
     </row>
     <row r="10">
@@ -532,10 +532,10 @@
         <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>2.5737828917859</v>
+        <v>2.57427956123471</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0722211548597914</v>
+        <v>0.0722298071945715</v>
       </c>
     </row>
     <row r="11">
@@ -546,10 +546,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>1.46754394593324</v>
+        <v>1.46756821441988</v>
       </c>
       <c r="D11" t="n">
-        <v>0.221908676469357</v>
+        <v>0.221914596352504</v>
       </c>
     </row>
     <row r="12">
@@ -560,10 +560,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>0.939262261327925</v>
+        <v>0.939235706664847</v>
       </c>
       <c r="D12" t="n">
-        <v>0.076588972054449</v>
+        <v>0.0765853287362225</v>
       </c>
     </row>
     <row r="13">
@@ -574,10 +574,10 @@
         <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>0.139326797297523</v>
+        <v>0.139357882061933</v>
       </c>
       <c r="D13" t="n">
-        <v>0.00657364646947169</v>
+        <v>0.00657574523047377</v>
       </c>
     </row>
     <row r="14">
@@ -588,7 +588,7 @@
         <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0230510669255519</v>
+        <v>0.0230564187299055</v>
       </c>
       <c r="D14"/>
     </row>
@@ -625,10 +625,10 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>54.114544741827</v>
+        <v>54.2920068185879</v>
       </c>
       <c r="D2" t="n">
-        <v>9.99633026927381</v>
+        <v>10.0359098723439</v>
       </c>
     </row>
     <row r="3">
@@ -639,10 +639,10 @@
         <v>13</v>
       </c>
       <c r="C3" t="n">
-        <v>24.4418564491065</v>
+        <v>24.3826543169154</v>
       </c>
       <c r="D3" t="n">
-        <v>0.235493426511848</v>
+        <v>0.234872224338485</v>
       </c>
     </row>
     <row r="4">
@@ -653,10 +653,10 @@
         <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>8.10872036568461</v>
+        <v>8.06688904755457</v>
       </c>
       <c r="D4" t="n">
-        <v>0.569988885259677</v>
+        <v>0.568106706627784</v>
       </c>
     </row>
     <row r="5">
@@ -667,10 +667,10 @@
         <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>3.7364525370258</v>
+        <v>3.72619530103943</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0604065991966392</v>
+        <v>0.0602198697114108</v>
       </c>
     </row>
     <row r="6">
@@ -681,10 +681,10 @@
         <v>11</v>
       </c>
       <c r="C6" t="n">
-        <v>3.2600262310611</v>
+        <v>3.2114875437113</v>
       </c>
       <c r="D6" t="n">
-        <v>0.381637481592593</v>
+        <v>0.372875239336723</v>
       </c>
     </row>
     <row r="7">
@@ -695,10 +695,10 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>2.38068014178256</v>
+        <v>2.37341644833467</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0576789885094573</v>
+        <v>0.0575256732831891</v>
       </c>
     </row>
     <row r="8">
@@ -709,10 +709,10 @@
         <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>1.44257685920316</v>
+        <v>1.43906660564869</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0493847440262116</v>
+        <v>0.0492352887412829</v>
       </c>
     </row>
     <row r="9">
@@ -723,10 +723,10 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>1.36767505041358</v>
+        <v>1.36450009279774</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0549577984573438</v>
+        <v>0.0548167936394943</v>
       </c>
     </row>
     <row r="10">
@@ -737,10 +737,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>0.509258253215987</v>
+        <v>0.508486644638778</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0463705023945219</v>
+        <v>0.0462714911307914</v>
       </c>
     </row>
     <row r="11">
@@ -751,10 +751,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>0.351612305902911</v>
+        <v>0.351483052903812</v>
       </c>
       <c r="D11" t="n">
-        <v>0.155646830278538</v>
+        <v>0.155638374117642</v>
       </c>
     </row>
     <row r="12">
@@ -765,10 +765,10 @@
         <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>0.226831131422201</v>
+        <v>0.224145730601667</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0102400978202364</v>
+        <v>0.0100082032877854</v>
       </c>
     </row>
     <row r="13">
@@ -779,10 +779,10 @@
         <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>0.031028231306782</v>
+        <v>0.0309894801565336</v>
       </c>
       <c r="D13" t="n">
-        <v>0.00584097358048779</v>
+        <v>0.00583147820982544</v>
       </c>
     </row>
     <row r="14">
@@ -793,10 +793,10 @@
         <v>14</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0287377020477431</v>
+        <v>0.0286789171097611</v>
       </c>
       <c r="D14" t="n">
-        <v>0.00414494693494354</v>
+        <v>0.0041369753964699</v>
       </c>
     </row>
   </sheetData>
